--- a/data/output/Timehistory_modal/3-1/响应统计结果.xlsx
+++ b/data/output/Timehistory_modal/3-1/响应统计结果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyFiles\GitHub\corner-point-response\data\output\Timehistory_modal\3-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD2A4CB-678C-45E4-9567-798AD042E43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7FFBCE2-BE53-478E-8BCA-6B39FF9891F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
   <si>
     <t>folder</t>
   </si>
@@ -144,6 +144,34 @@
   </si>
   <si>
     <t>Model4_10yr_090</t>
+  </si>
+  <si>
+    <t>matlab</t>
+  </si>
+  <si>
+    <t>集中质量模型</t>
+  </si>
+  <si>
+    <t>SAP2000模型</t>
+  </si>
+  <si>
+    <t>偏差(%)</t>
+  </si>
+  <si>
+    <t>角度</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>3-1模型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1899,9 +1927,327 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C946EDA7-C100-4E72-BC4E-F4E26BAE35CD}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>0.131909159254782</v>
+      </c>
+      <c r="C4">
+        <v>5.8929978706446999E-2</v>
+      </c>
+      <c r="D4">
+        <v>0.13358617856798699</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>8.7266463000000002E-2</v>
+      </c>
+      <c r="B5">
+        <v>0.12898370366826101</v>
+      </c>
+      <c r="C5">
+        <v>5.1537770390811401E-2</v>
+      </c>
+      <c r="D5">
+        <v>0.12966659916158399</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>0.17453292500000001</v>
+      </c>
+      <c r="B6">
+        <v>0.118551883928231</v>
+      </c>
+      <c r="C6">
+        <v>5.8047353042828001E-2</v>
+      </c>
+      <c r="D6">
+        <v>0.119775740231519</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0.26179938800000002</v>
+      </c>
+      <c r="B7">
+        <v>0.12546483785543</v>
+      </c>
+      <c r="C7">
+        <v>5.7835183041979599E-2</v>
+      </c>
+      <c r="D7">
+        <v>0.12658099419575999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>0.34906585000000001</v>
+      </c>
+      <c r="B8">
+        <v>0.109851110046099</v>
+      </c>
+      <c r="C8">
+        <v>5.5763385548076499E-2</v>
+      </c>
+      <c r="D8">
+        <v>0.11101559533019099</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>0.43633231300000003</v>
+      </c>
+      <c r="B9">
+        <v>0.103682403408451</v>
+      </c>
+      <c r="C9">
+        <v>5.3359426887002501E-2</v>
+      </c>
+      <c r="D9">
+        <v>0.10498600694860399</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>0.52359877600000004</v>
+      </c>
+      <c r="B10">
+        <v>9.5155221765517495E-2</v>
+      </c>
+      <c r="C10">
+        <v>4.4559973968942103E-2</v>
+      </c>
+      <c r="D10">
+        <v>9.6144885824918702E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>0.61086523800000003</v>
+      </c>
+      <c r="B11">
+        <v>9.6461739738963298E-2</v>
+      </c>
+      <c r="C11">
+        <v>4.1297125367470301E-2</v>
+      </c>
+      <c r="D11">
+        <v>9.7416716702063103E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>0.69813170099999999</v>
+      </c>
+      <c r="B12">
+        <v>8.6638852201837396E-2</v>
+      </c>
+      <c r="C12">
+        <v>4.1365270696212902E-2</v>
+      </c>
+      <c r="D12">
+        <v>8.7891175624806597E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0.78539816299999998</v>
+      </c>
+      <c r="B13">
+        <v>8.3705154307353202E-2</v>
+      </c>
+      <c r="C13">
+        <v>3.8890644140651999E-2</v>
+      </c>
+      <c r="D13">
+        <v>8.5070690443153699E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>0.87266462600000005</v>
+      </c>
+      <c r="B14">
+        <v>7.7279307898750899E-2</v>
+      </c>
+      <c r="C14">
+        <v>3.7674369178060801E-2</v>
+      </c>
+      <c r="D14">
+        <v>7.87923861843388E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>0.95993108900000002</v>
+      </c>
+      <c r="B15">
+        <v>8.5003022373929496E-2</v>
+      </c>
+      <c r="C15">
+        <v>3.7717864736939499E-2</v>
+      </c>
+      <c r="D15">
+        <v>8.65759036183254E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1.047197551</v>
+      </c>
+      <c r="B16">
+        <v>8.4245058862609107E-2</v>
+      </c>
+      <c r="C16">
+        <v>3.4952894680732503E-2</v>
+      </c>
+      <c r="D16">
+        <v>8.5811466447113696E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1.134464014</v>
+      </c>
+      <c r="B17">
+        <v>8.8504795253157895E-2</v>
+      </c>
+      <c r="C17">
+        <v>3.5459123608468097E-2</v>
+      </c>
+      <c r="D17">
+        <v>8.9834381647751704E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1.2217304760000001</v>
+      </c>
+      <c r="B18">
+        <v>8.61500564074833E-2</v>
+      </c>
+      <c r="C18">
+        <v>4.0025310074388198E-2</v>
+      </c>
+      <c r="D18">
+        <v>8.7846676258970594E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1.308996939</v>
+      </c>
+      <c r="B19">
+        <v>9.81709786644379E-2</v>
+      </c>
+      <c r="C19">
+        <v>4.0218462935227503E-2</v>
+      </c>
+      <c r="D19">
+        <v>0.100015712124532</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1.396263402</v>
+      </c>
+      <c r="B20">
+        <v>0.118880303918294</v>
+      </c>
+      <c r="C20">
+        <v>4.4338198993811397E-2</v>
+      </c>
+      <c r="D20">
+        <v>0.120565536929489</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1.4835298640000001</v>
+      </c>
+      <c r="B21">
+        <v>0.110334335989004</v>
+      </c>
+      <c r="C21">
+        <v>4.6123161941655499E-2</v>
+      </c>
+      <c r="D21">
+        <v>0.112551701534839</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1.570796327</v>
+      </c>
+      <c r="B22">
+        <v>0.12877187494522599</v>
+      </c>
+      <c r="C22">
+        <v>4.5901941428107697E-2</v>
+      </c>
+      <c r="D22">
+        <v>0.13088670980851999</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
